--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\новый_бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F80CE1-D558-42EC-99D0-C3F1F4950C55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C46BB0-4C43-4F85-8A3C-72855F0ED88C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мелитополь" sheetId="1" r:id="rId1"/>
     <sheet name="Бердянск" sheetId="2" r:id="rId2"/>
     <sheet name="Донецк" sheetId="3" r:id="rId3"/>
     <sheet name="Луганск" sheetId="4" r:id="rId4"/>
+    <sheet name="Мариуполь" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Бердянск!$A$3:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Донецк!$A$3:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Луганск!$A$3:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Мариуполь!$A$3:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Мелитополь!$A$3:$I$52</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="77">
   <si>
     <t>Артикул</t>
   </si>
@@ -6758,4 +6760,1472 @@
   <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C708EE14-0F30-4B69-95F4-6DFC5AF5DE31}">
+  <dimension ref="A1:I58"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10" style="4" customWidth="1"/>
+    <col min="2" max="2" width="90.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="4" customWidth="1"/>
+    <col min="4" max="5" width="21.5703125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.85546875" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" ht="38.25">
+      <c r="A2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A4" s="1">
+        <v>5038435</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="10">
+        <v>10</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="11">
+        <f>D4/C4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H4" s="11">
+        <f>G4*D4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A5" s="33">
+        <v>8783323</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="28">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="11">
+        <f>E5/5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="H5" s="21">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" s="23" customFormat="1" ht="25.5">
+      <c r="A6" s="1">
+        <v>5038459</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11">
+        <f>D6/C6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6*D6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A7" s="33">
+        <v>8785235</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="10">
+        <v>5</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="11">
+        <f>E7/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="11">
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A8" s="1">
+        <v>5038411</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="10">
+        <v>10</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="11">
+        <f>D8/C8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H8" s="11">
+        <f>G8*D8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A9" s="2">
+        <v>8785242</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="10">
+        <v>5</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="11">
+        <f>E9/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="11">
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A10" s="1">
+        <v>5038398</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="10">
+        <v>10</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="11">
+        <f>D10/C10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H10" s="11">
+        <f>G10*D10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A11" s="2">
+        <v>8785259</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="10">
+        <v>5</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="11">
+        <f>E11/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="11">
+        <f>E11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A12" s="2">
+        <v>5038855</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="10">
+        <v>10</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="11">
+        <f>D12/C12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="11">
+        <f>G12*D12</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" s="13" customFormat="1" ht="25.5">
+      <c r="A13" s="2">
+        <v>5038831</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="25">
+        <v>10</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11">
+        <f>D13/C13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H13" s="11">
+        <f>G13*D13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="38.25">
+      <c r="A14" s="26">
+        <v>8784931</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="25">
+        <v>5</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="11">
+        <f>E14/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H14" s="11">
+        <f>E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="13" customFormat="1">
+      <c r="A15" s="2">
+        <v>1018950</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="10">
+        <v>10</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="11">
+        <f>D15/C15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H15" s="11">
+        <f t="shared" ref="H15:H23" si="0">G15*D15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" s="13" customFormat="1">
+      <c r="A16" s="2">
+        <v>1018967</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="10">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="11">
+        <f>D16/C16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H16" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" s="13" customFormat="1">
+      <c r="A17" s="2">
+        <v>8444194</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10">
+        <v>6</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="11">
+        <f t="shared" ref="F17:F23" si="1">D17/C17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" s="13" customFormat="1">
+      <c r="A18" s="2">
+        <v>8444187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="10">
+        <v>6</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" s="13" customFormat="1">
+      <c r="A19" s="2">
+        <v>8444163</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="10">
+        <v>8</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" s="13" customFormat="1">
+      <c r="A20" s="2">
+        <v>8444170</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="10">
+        <v>8</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="11">
+        <f>D20/C20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" s="13" customFormat="1">
+      <c r="A21" s="2">
+        <v>9988377</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="10">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H21" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" s="13" customFormat="1">
+      <c r="A22" s="2">
+        <v>9988391</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="10">
+        <v>16</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H22" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" s="13" customFormat="1">
+      <c r="A23" s="2">
+        <v>5034819</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="10">
+        <v>6</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H23" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" s="13" customFormat="1">
+      <c r="A24" s="2">
+        <v>2981244</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="10">
+        <v>6</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="11">
+        <f>E24/7.8</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="H24" s="11">
+        <f>E24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="13" customFormat="1">
+      <c r="A25" s="2">
+        <v>8785198</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="10">
+        <v>5</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="11">
+        <f>E25/16.5</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="H25" s="11">
+        <f>E25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="13" customFormat="1">
+      <c r="A26" s="2">
+        <v>9988452</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="10">
+        <v>8</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="11">
+        <f t="shared" ref="F26:F37" si="2">D26/C26</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="H26" s="11">
+        <f t="shared" ref="H26:H31" si="3">G26*D26</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" s="13" customFormat="1">
+      <c r="A27" s="2">
+        <v>9988476</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="10">
+        <v>28</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="H27" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11"/>
+    </row>
+    <row r="28" spans="1:9" s="13" customFormat="1">
+      <c r="A28" s="2">
+        <v>9988681</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="10">
+        <v>16</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="11">
+        <f>D28/C28</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H28" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" spans="1:9" s="13" customFormat="1">
+      <c r="A29" s="2">
+        <v>9988438</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="10">
+        <v>16</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H29" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:9" s="13" customFormat="1">
+      <c r="A30" s="2">
+        <v>9988445</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="10">
+        <v>16</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H30" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" spans="1:9" s="13" customFormat="1">
+      <c r="A31" s="2">
+        <v>9988421</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="10">
+        <v>16</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H31" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:9" s="13" customFormat="1">
+      <c r="A32" s="2">
+        <v>9988674</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="10">
+        <v>16</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H32" s="11">
+        <f>D32*G32</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" s="13" customFormat="1">
+      <c r="A33" s="26">
+        <v>8444903</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="10">
+        <v>8</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H33" s="11">
+        <f>D33*G33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" s="13" customFormat="1">
+      <c r="A34" s="26">
+        <v>8444910</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="10">
+        <v>8</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H34" s="11">
+        <f>D34*G34</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" s="13" customFormat="1">
+      <c r="A35" s="26">
+        <v>8444927</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="10">
+        <v>8</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="11">
+        <f>D35*G35</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" spans="1:9" s="13" customFormat="1">
+      <c r="A36" s="2">
+        <v>8445160</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="10">
+        <v>8</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="11">
+        <f>G36*D36</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" s="13" customFormat="1">
+      <c r="A37" s="2">
+        <v>8445177</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="10">
+        <v>8</v>
+      </c>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="11">
+        <f>G37*D37</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" spans="1:9" s="13" customFormat="1">
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="10">
+        <v>10</v>
+      </c>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="11">
+        <f>D38/C38</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="11">
+        <f>G38*D38</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" spans="1:9" s="13" customFormat="1">
+      <c r="A39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="10">
+        <v>4</v>
+      </c>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="11">
+        <f>E39/15</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H39" s="11">
+        <f>E39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="29" customFormat="1">
+      <c r="A40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="10">
+        <v>10</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="11">
+        <f>D40/C40</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H40" s="11">
+        <f>G40*D40</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" s="29" customFormat="1" ht="11.25" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="10">
+        <v>4</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="11">
+        <f>E41/15</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H41" s="11">
+        <f>E41</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="13" customFormat="1">
+      <c r="A42" s="2">
+        <v>7100108</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="10">
+        <v>12</v>
+      </c>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="11">
+        <f>D42/C42</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="11">
+        <f>D42*G42</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="11"/>
+    </row>
+    <row r="43" spans="1:9" s="13" customFormat="1">
+      <c r="A43" s="2">
+        <v>7100139</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="10">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="11">
+        <f>E43/20</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H43" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="13" customFormat="1">
+      <c r="A44" s="2">
+        <v>7100740</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="10">
+        <v>12</v>
+      </c>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="11">
+        <f>D44/C44</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H44" s="11">
+        <f>D44*G44</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="11"/>
+    </row>
+    <row r="45" spans="1:9" s="13" customFormat="1">
+      <c r="A45" s="2">
+        <v>7100726</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="10">
+        <v>8</v>
+      </c>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="11">
+        <f>E45/20</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H45" s="11">
+        <f>E45</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="13" customFormat="1">
+      <c r="A46" s="2">
+        <v>4421584</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="10">
+        <v>12</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="11">
+        <f>D46/C46</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H46" s="11">
+        <f>G46*D46</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" spans="1:9" s="13" customFormat="1">
+      <c r="A47" s="2">
+        <v>4421577</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="10">
+        <v>12</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="11">
+        <f>D47/C47</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H47" s="11">
+        <f>G47*D47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" spans="1:9" s="13" customFormat="1">
+      <c r="A48" s="2">
+        <v>9985949</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="10">
+        <v>10</v>
+      </c>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="11">
+        <f>D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="18">
+        <v>1</v>
+      </c>
+      <c r="H48" s="11">
+        <f>G48*D48</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" spans="1:9" s="13" customFormat="1">
+      <c r="A49" s="2">
+        <v>8786928</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="10">
+        <v>4</v>
+      </c>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="11">
+        <f>E49/6</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="H49" s="11">
+        <f>E49</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="13" customFormat="1">
+      <c r="A50" s="2">
+        <v>6948270</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="10">
+        <v>12</v>
+      </c>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="11">
+        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0.372</v>
+      </c>
+      <c r="H50" s="11">
+        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="11"/>
+    </row>
+    <row r="51" spans="1:9" s="13" customFormat="1">
+      <c r="A51" s="2">
+        <v>6948287</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="10">
+        <v>12</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="12">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="H51" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="11"/>
+    </row>
+    <row r="52" spans="1:9" s="13" customFormat="1">
+      <c r="A52" s="2">
+        <v>6948256</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="10">
+        <v>12</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="12">
+        <v>0.372</v>
+      </c>
+      <c r="H52" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53" spans="1:9" s="13" customFormat="1">
+      <c r="A53" s="2">
+        <v>6948263</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="10">
+        <v>12</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="H53" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="11"/>
+    </row>
+    <row r="54" spans="1:9" s="13" customFormat="1">
+      <c r="A54" s="2">
+        <v>6948249</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="10">
+        <v>12</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="H54" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="11"/>
+    </row>
+    <row r="55" spans="1:9" s="13" customFormat="1">
+      <c r="A55" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="10">
+        <v>24</v>
+      </c>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11"/>
+    </row>
+    <row r="56" spans="1:9" s="13" customFormat="1">
+      <c r="A56" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="10">
+        <v>24</v>
+      </c>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G56" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H56" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="11"/>
+    </row>
+    <row r="57" spans="1:9" s="13" customFormat="1">
+      <c r="A57" s="15">
+        <v>1103201</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="10">
+        <v>24</v>
+      </c>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G57" s="12">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H57" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="11"/>
+    </row>
+    <row r="58" spans="1:9" s="13" customFormat="1">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="11"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="3">
+        <f>SUM(H4:H57)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="11"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр  дистр.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\новый_бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C46BB0-4C43-4F85-8A3C-72855F0ED88C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0CDE88-D93B-45B7-836F-B971382CB6AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мелитополь" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Бердянск!$A$3:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Донецк!$A$3:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Луганск!$A$3:$I$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Мариуполь!$A$3:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Мариуполь!$A$3:$I$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Мелитополь!$A$3:$I$52</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -200,12 +200,6 @@
     <t>783К825</t>
   </si>
   <si>
-    <t>Спред растительно-сливочный «Сливочный вкус» 82,5% 180гр</t>
-  </si>
-  <si>
-    <t>Спред растительно-сливочный «Сливочный вкус» 72,5% 180гр</t>
-  </si>
-  <si>
     <t>Сырный продукт Моцарелла 45% (батоны) 1,0кг ТМ "КОРОВИНО"</t>
   </si>
   <si>
@@ -271,12 +265,18 @@
   <si>
     <t>Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток</t>
   </si>
+  <si>
+    <t>Майонез провансаль классический с массовой долей жира 67% ТМ «ПАПА МОЖЕТ» 186г дой-пак с дозатором</t>
+  </si>
+  <si>
+    <t>Майонез провансаль классический оливковый с массовой долей жира 67% ТМ «ПАПА МОЖЕТ» 186г дой-пак с дозатором</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -390,6 +390,12 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Cyr"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -444,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -513,6 +519,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -990,7 +999,7 @@
         <v>8783323</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="28">
         <v>4</v>
@@ -1040,7 +1049,7 @@
         <v>8785235</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10">
         <v>5</v>
@@ -1219,7 +1228,7 @@
         <v>8784931</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -1371,7 +1380,7 @@
         <v>8444170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="10">
         <v>8</v>
@@ -1775,7 +1784,7 @@
         <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10">
         <v>8</v>
@@ -1800,7 +1809,7 @@
         <v>8445177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -1929,7 +1938,7 @@
         <v>7100108</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C42" s="10">
         <v>12</v>
@@ -1954,7 +1963,7 @@
         <v>7100139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C43" s="10">
         <v>8</v>
@@ -1973,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
@@ -1981,7 +1990,7 @@
         <v>7100740</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" s="10">
         <v>12</v>
@@ -2006,7 +2015,7 @@
         <v>7100726</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="10">
         <v>8</v>
@@ -2025,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
       <c r="A46" s="2">
-        <v>4421584</v>
+        <v>9985949</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -2044,8 +2053,8 @@
         <f>D46/C46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="12">
-        <v>0.18</v>
+      <c r="G46" s="18">
+        <v>1</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -2055,84 +2064,84 @@
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
       <c r="A47" s="2">
-        <v>4421577</v>
+        <v>8786928</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>D47/C47</f>
+        <f>E47/6</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>0.18</v>
+        <v>1.5</v>
       </c>
       <c r="H47" s="11">
-        <f>G47*D47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11"/>
+        <f>E47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>9985949</v>
+        <v>6948270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C48" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11">
-        <f>D48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="18">
-        <v>1</v>
+        <f t="shared" ref="F48:F57" si="4">D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.372</v>
       </c>
       <c r="H48" s="11">
-        <f>G48*D48</f>
+        <f t="shared" ref="H48:H57" si="5">G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>8786928</v>
+        <v>6948287</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>1.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H49" s="11">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>58</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>6948270</v>
+        <v>6948256</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>59</v>
@@ -2143,21 +2152,21 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="12">
         <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>6948287</v>
+        <v>6948263</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>60</v>
@@ -2182,7 +2191,7 @@
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>6948256</v>
+        <v>6948249</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>61</v>
@@ -2197,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="H52" s="11">
         <f t="shared" si="5"/>
@@ -2206,14 +2215,14 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
-      <c r="A53" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
+      <c r="A53" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C53" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
@@ -2222,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.74399999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="11">
         <f t="shared" si="5"/>
@@ -2231,14 +2240,14 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
-      <c r="A54" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
+      <c r="A54" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
@@ -2247,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="11">
         <f t="shared" si="5"/>
@@ -2257,7 +2266,7 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="15">
-        <v>2105201</v>
+        <v>1103201</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>74</v>
@@ -2272,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.1</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="5"/>
@@ -2282,24 +2291,24 @@
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="15">
-        <v>2103201</v>
+        <v>6948362</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="10">
-        <v>24</v>
-      </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="11">
+      <c r="C56" s="35">
+        <v>20</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H56" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2307,24 +2316,24 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="15">
-        <v>1103201</v>
+        <v>6948508</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="10">
-        <v>24</v>
-      </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="11">
+      <c r="C57" s="35">
+        <v>20</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="12">
-        <v>5.5E-2</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2464,7 +2473,7 @@
         <v>8783323</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="28">
         <v>4</v>
@@ -2514,7 +2523,7 @@
         <v>8785235</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10">
         <v>5</v>
@@ -2693,7 +2702,7 @@
         <v>8784931</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -2845,7 +2854,7 @@
         <v>8444170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="10">
         <v>8</v>
@@ -3249,7 +3258,7 @@
         <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10">
         <v>8</v>
@@ -3274,7 +3283,7 @@
         <v>8445177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -3403,7 +3412,7 @@
         <v>7100108</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C42" s="10">
         <v>12</v>
@@ -3428,7 +3437,7 @@
         <v>7100139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C43" s="10">
         <v>8</v>
@@ -3447,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
@@ -3455,7 +3464,7 @@
         <v>7100740</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" s="10">
         <v>12</v>
@@ -3480,7 +3489,7 @@
         <v>7100726</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="10">
         <v>8</v>
@@ -3499,18 +3508,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
       <c r="A46" s="2">
-        <v>4421584</v>
+        <v>9985949</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -3518,8 +3527,8 @@
         <f>D46/C46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="12">
-        <v>0.18</v>
+      <c r="G46" s="18">
+        <v>1</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -3529,84 +3538,84 @@
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
       <c r="A47" s="2">
-        <v>4421577</v>
+        <v>8786928</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>D47/C47</f>
+        <f>E47/6</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>0.18</v>
+        <v>1.5</v>
       </c>
       <c r="H47" s="11">
-        <f>G47*D47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11"/>
+        <f>E47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>9985949</v>
+        <v>6948270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C48" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11">
-        <f>D48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="18">
-        <v>1</v>
+        <f t="shared" ref="F48:F57" si="4">D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.372</v>
       </c>
       <c r="H48" s="11">
-        <f>G48*D48</f>
+        <f t="shared" ref="H48:H57" si="5">G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>8786928</v>
+        <v>6948287</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>1.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H49" s="11">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>58</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>6948270</v>
+        <v>6948256</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>59</v>
@@ -3617,21 +3626,21 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="12">
         <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>6948287</v>
+        <v>6948263</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>60</v>
@@ -3656,7 +3665,7 @@
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>6948256</v>
+        <v>6948249</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>61</v>
@@ -3671,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="H52" s="11">
         <f t="shared" si="5"/>
@@ -3680,14 +3689,14 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
-      <c r="A53" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
+      <c r="A53" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C53" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
@@ -3696,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.74399999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="11">
         <f t="shared" si="5"/>
@@ -3705,14 +3714,14 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
-      <c r="A54" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
+      <c r="A54" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
@@ -3721,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="11">
         <f t="shared" si="5"/>
@@ -3731,7 +3740,7 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="15">
-        <v>2105201</v>
+        <v>1103201</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>74</v>
@@ -3746,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.1</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="5"/>
@@ -3756,24 +3765,24 @@
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="15">
-        <v>2103201</v>
+        <v>6948362</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="10">
-        <v>24</v>
-      </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="11">
+      <c r="C56" s="35">
+        <v>20</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H56" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3781,24 +3790,24 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="15">
-        <v>1103201</v>
+        <v>6948508</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="10">
-        <v>24</v>
-      </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="11">
+      <c r="C57" s="35">
+        <v>20</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="12">
-        <v>5.5E-2</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3932,7 +3941,7 @@
         <v>8783323</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="28">
         <v>4</v>
@@ -3982,7 +3991,7 @@
         <v>8785235</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10">
         <v>5</v>
@@ -4161,7 +4170,7 @@
         <v>8784931</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -4313,7 +4322,7 @@
         <v>8444170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="10">
         <v>8</v>
@@ -4717,7 +4726,7 @@
         <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10">
         <v>8</v>
@@ -4742,7 +4751,7 @@
         <v>8445177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -4871,7 +4880,7 @@
         <v>7100108</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C42" s="10">
         <v>12</v>
@@ -4896,7 +4905,7 @@
         <v>7100139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C43" s="10">
         <v>8</v>
@@ -4915,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
@@ -4923,7 +4932,7 @@
         <v>7100740</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" s="10">
         <v>12</v>
@@ -4948,7 +4957,7 @@
         <v>7100726</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="10">
         <v>8</v>
@@ -4967,18 +4976,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
       <c r="A46" s="2">
-        <v>4421584</v>
+        <v>9985949</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -4986,8 +4995,8 @@
         <f>D46/C46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="12">
-        <v>0.18</v>
+      <c r="G46" s="18">
+        <v>1</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -4997,84 +5006,84 @@
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
       <c r="A47" s="2">
-        <v>4421577</v>
+        <v>8786928</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>D47/C47</f>
+        <f>E47/6</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>0.18</v>
+        <v>1.5</v>
       </c>
       <c r="H47" s="11">
-        <f>G47*D47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11"/>
+        <f>E47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>9985949</v>
+        <v>6948270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C48" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11">
-        <f>D48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="18">
-        <v>1</v>
+        <f t="shared" ref="F48:F57" si="4">D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.372</v>
       </c>
       <c r="H48" s="11">
-        <f>G48*D48</f>
+        <f t="shared" ref="H48:H57" si="5">G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>8786928</v>
+        <v>6948287</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>1.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H49" s="11">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>58</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>6948270</v>
+        <v>6948256</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>59</v>
@@ -5085,21 +5094,21 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="12">
         <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>6948287</v>
+        <v>6948263</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>60</v>
@@ -5124,7 +5133,7 @@
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>6948256</v>
+        <v>6948249</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>61</v>
@@ -5139,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="H52" s="11">
         <f t="shared" si="5"/>
@@ -5148,14 +5157,14 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
-      <c r="A53" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
+      <c r="A53" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C53" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
@@ -5164,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.74399999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="11">
         <f t="shared" si="5"/>
@@ -5173,14 +5182,14 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
-      <c r="A54" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
+      <c r="A54" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
@@ -5189,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="11">
         <f t="shared" si="5"/>
@@ -5199,7 +5208,7 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="15">
-        <v>2105201</v>
+        <v>1103201</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>74</v>
@@ -5214,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.1</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="5"/>
@@ -5224,24 +5233,24 @@
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="15">
-        <v>2103201</v>
+        <v>6948362</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="10">
-        <v>24</v>
-      </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="11">
+      <c r="C56" s="35">
+        <v>20</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H56" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5249,24 +5258,24 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="15">
-        <v>1103201</v>
+        <v>6948508</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="10">
-        <v>24</v>
-      </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="11">
+      <c r="C57" s="35">
+        <v>20</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="12">
-        <v>5.5E-2</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5400,7 +5409,7 @@
         <v>8783323</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="28">
         <v>4</v>
@@ -5450,7 +5459,7 @@
         <v>8785235</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10">
         <v>5</v>
@@ -5629,7 +5638,7 @@
         <v>8784931</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -5781,7 +5790,7 @@
         <v>8444170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="10">
         <v>8</v>
@@ -6185,7 +6194,7 @@
         <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10">
         <v>8</v>
@@ -6210,7 +6219,7 @@
         <v>8445177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -6339,7 +6348,7 @@
         <v>7100108</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C42" s="10">
         <v>12</v>
@@ -6364,7 +6373,7 @@
         <v>7100139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C43" s="10">
         <v>8</v>
@@ -6383,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
@@ -6391,7 +6400,7 @@
         <v>7100740</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" s="10">
         <v>12</v>
@@ -6416,7 +6425,7 @@
         <v>7100726</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="10">
         <v>8</v>
@@ -6435,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
       <c r="A46" s="2">
-        <v>4421584</v>
+        <v>9985949</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -6454,8 +6463,8 @@
         <f>D46/C46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="12">
-        <v>0.18</v>
+      <c r="G46" s="18">
+        <v>1</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -6465,84 +6474,84 @@
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
       <c r="A47" s="2">
-        <v>4421577</v>
+        <v>8786928</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>D47/C47</f>
+        <f>E47/6</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>0.18</v>
+        <v>1.5</v>
       </c>
       <c r="H47" s="11">
-        <f>G47*D47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11"/>
+        <f>E47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>9985949</v>
+        <v>6948270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C48" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11">
-        <f>D48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="18">
-        <v>1</v>
+        <f t="shared" ref="F48:F57" si="4">D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.372</v>
       </c>
       <c r="H48" s="11">
-        <f>G48*D48</f>
+        <f t="shared" ref="H48:H57" si="5">G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>8786928</v>
+        <v>6948287</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>1.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H49" s="11">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>58</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>6948270</v>
+        <v>6948256</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>59</v>
@@ -6553,21 +6562,21 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="12">
         <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>6948287</v>
+        <v>6948263</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>60</v>
@@ -6592,7 +6601,7 @@
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>6948256</v>
+        <v>6948249</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>61</v>
@@ -6607,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="H52" s="11">
         <f t="shared" si="5"/>
@@ -6616,14 +6625,14 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
-      <c r="A53" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
+      <c r="A53" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C53" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
@@ -6632,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.74399999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="11">
         <f t="shared" si="5"/>
@@ -6641,14 +6650,14 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
-      <c r="A54" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
+      <c r="A54" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
@@ -6657,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="11">
         <f t="shared" si="5"/>
@@ -6667,7 +6676,7 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="15">
-        <v>2105201</v>
+        <v>1103201</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>74</v>
@@ -6682,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.1</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="5"/>
@@ -6692,24 +6701,24 @@
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="15">
-        <v>2103201</v>
+        <v>6948362</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="10">
-        <v>24</v>
-      </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="11">
+      <c r="C56" s="35">
+        <v>20</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H56" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6717,24 +6726,24 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="15">
-        <v>1103201</v>
+        <v>6948508</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="10">
-        <v>24</v>
-      </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="11">
+      <c r="C57" s="35">
+        <v>20</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="12">
-        <v>5.5E-2</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6868,7 +6877,7 @@
         <v>8783323</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="28">
         <v>4</v>
@@ -6918,7 +6927,7 @@
         <v>8785235</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10">
         <v>5</v>
@@ -7097,7 +7106,7 @@
         <v>8784931</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -7249,7 +7258,7 @@
         <v>8444170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="10">
         <v>8</v>
@@ -7653,7 +7662,7 @@
         <v>8445160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10">
         <v>8</v>
@@ -7678,7 +7687,7 @@
         <v>8445177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10">
         <v>8</v>
@@ -7807,7 +7816,7 @@
         <v>7100108</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C42" s="10">
         <v>12</v>
@@ -7832,7 +7841,7 @@
         <v>7100139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C43" s="10">
         <v>8</v>
@@ -7851,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
@@ -7859,7 +7868,7 @@
         <v>7100740</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" s="10">
         <v>12</v>
@@ -7884,7 +7893,7 @@
         <v>7100726</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="10">
         <v>8</v>
@@ -7903,18 +7912,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
       <c r="A46" s="2">
-        <v>4421584</v>
+        <v>9985949</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
@@ -7922,8 +7931,8 @@
         <f>D46/C46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="12">
-        <v>0.18</v>
+      <c r="G46" s="18">
+        <v>1</v>
       </c>
       <c r="H46" s="11">
         <f>G46*D46</f>
@@ -7933,84 +7942,84 @@
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1">
       <c r="A47" s="2">
-        <v>4421577</v>
+        <v>8786928</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11">
-        <f>D47/C47</f>
+        <f>E47/6</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>0.18</v>
+        <v>1.5</v>
       </c>
       <c r="H47" s="11">
-        <f>G47*D47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="11"/>
+        <f>E47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="48" spans="1:9" s="13" customFormat="1">
       <c r="A48" s="2">
-        <v>9985949</v>
+        <v>6948270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C48" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11">
-        <f>D48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="18">
-        <v>1</v>
+        <f t="shared" ref="F48:F57" si="4">D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.372</v>
       </c>
       <c r="H48" s="11">
-        <f>G48*D48</f>
+        <f t="shared" ref="H48:H57" si="5">G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
       <c r="A49" s="2">
-        <v>8786928</v>
+        <v>6948287</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11">
-        <f>E49/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>1.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H49" s="11">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>58</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" s="13" customFormat="1">
       <c r="A50" s="2">
-        <v>6948270</v>
+        <v>6948256</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>59</v>
@@ -8021,21 +8030,21 @@
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11">
-        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="12">
         <v>0.372</v>
       </c>
       <c r="H50" s="11">
-        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" s="13" customFormat="1">
       <c r="A51" s="2">
-        <v>6948287</v>
+        <v>6948263</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>60</v>
@@ -8060,7 +8069,7 @@
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
       <c r="A52" s="2">
-        <v>6948256</v>
+        <v>6948249</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>61</v>
@@ -8075,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="H52" s="11">
         <f t="shared" si="5"/>
@@ -8084,14 +8093,14 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" s="13" customFormat="1">
-      <c r="A53" s="2">
-        <v>6948263</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
+      <c r="A53" s="15">
+        <v>2105201</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C53" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
@@ -8100,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.74399999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="11">
         <f t="shared" si="5"/>
@@ -8109,14 +8118,14 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
-      <c r="A54" s="2">
-        <v>6948249</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
+      <c r="A54" s="15">
+        <v>2103201</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="C54" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
@@ -8125,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="11">
         <f t="shared" si="5"/>
@@ -8135,7 +8144,7 @@
     </row>
     <row r="55" spans="1:9" s="13" customFormat="1">
       <c r="A55" s="15">
-        <v>2105201</v>
+        <v>1103201</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>74</v>
@@ -8150,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.1</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="5"/>
@@ -8160,24 +8169,24 @@
     </row>
     <row r="56" spans="1:9" s="13" customFormat="1">
       <c r="A56" s="15">
-        <v>2103201</v>
+        <v>6948362</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="10">
-        <v>24</v>
-      </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="11">
+      <c r="C56" s="35">
+        <v>20</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H56" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -8185,24 +8194,24 @@
     </row>
     <row r="57" spans="1:9" s="13" customFormat="1">
       <c r="A57" s="15">
-        <v>1103201</v>
+        <v>6948508</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="10">
-        <v>24</v>
-      </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="11">
+      <c r="C57" s="35">
+        <v>20</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="12">
-        <v>5.5E-2</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -8225,7 +8234,7 @@
       <c r="I58" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I52" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A3:I50" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>